--- a/assets/constructions/examples/ctd_mie_3075.xlsx
+++ b/assets/constructions/examples/ctd_mie_3075.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,171 +579,211 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>032W90845-03-06-025100</t>
+          <t>M1200D025Z02A25HN07L200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M1200MINI</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>33.7</v>
       </c>
       <c r="E2" t="n">
-        <v>29.1</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.375</v>
+        <v>0.72</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ON...05 | SN...12</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>HB-25</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>PALB_ON0505H|PALB_SN1206H</t>
+          <t>WIDIA_XHN0704H</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>45</v>
       </c>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>WID_XHN0704_H</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>WID_M1200D_20</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R245-080A32-12L</t>
+          <t>M1200D025Z03A20HN07L120</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 245 face milling cutter</t>
+          <t>M1200MINI</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>92.5</v>
+        <v>33.7</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>120</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>12700</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>0.28</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CoroMill 245 -size 12 (R245-12T3)</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>COR_R245-12T3H</t>
+          <t>WIDIA_XHN0704H</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -756,20 +796,30 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>SAND_R245-12T3_H</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+          <t>WID_XHN0704_H</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>WID_M1200D_20</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M1200D025Z03A20HN07L120</t>
+          <t>12396202200</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -779,43 +829,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M1200MINI</t>
+          <t>M660</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
         <v>25</v>
       </c>
-      <c r="F4" t="n">
-        <v>20</v>
-      </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>6.35</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
@@ -823,19 +873,19 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>WIDIA_XHN0704H</t>
+          <t>WIDIA_XSN1205H</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -845,7 +895,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="Z4" t="n">
@@ -854,12 +904,12 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>WID_XHN0704_H</t>
+          <t>WID_XSN1205_H</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>WID_M1200D_20</t>
+          <t>WID_123962_2907</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -867,83 +917,89 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M1200D032Z03A25HN07L130</t>
+          <t>R245-063A32-12M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M1200MINI</t>
+          <t>CoroMillⓇ 245 face milling cutter</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.7</v>
+        <v>75.5</v>
       </c>
       <c r="E5" t="n">
+        <v>63</v>
+      </c>
+      <c r="F5" t="n">
         <v>32</v>
       </c>
-      <c r="F5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" t="n">
-        <v>130</v>
-      </c>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>120</v>
+      </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>17600</v>
-      </c>
-      <c r="N5" t="b">
+        <v>14400</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CoroMill 245 -size 12 (R245-12T3)</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>HA-32</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>COR_R245-12T3H</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>HA-25</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>WIDIA_XHN0704H</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -956,24 +1012,26 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>WID_XHN0704_H</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>WID_M1200D_46</t>
-        </is>
-      </c>
+          <t>SAND_R245-12T3_H</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M1200D040Z04B25HN09</t>
+          <t>M1200D025Z03B20HN07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -983,43 +1041,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M1200</t>
+          <t>M1200MINI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>33.7</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>15800</v>
+        <v>20000</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
@@ -1027,12 +1085,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>HB-25</t>
+          <t>HB-20</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>WIDIA_XHN0905H</t>
+          <t>WIDIA_XHN0704H</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1058,7 +1116,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>WID_XHN0905_H</t>
+          <t>WID_XHN0704_H</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1071,6 +1129,12 @@
           <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
